--- a/物资/CavePI水下机器人BOM.xlsx
+++ b/物资/CavePI水下机器人BOM.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM主表" sheetId="1" r:id="R9df5fd07afbb4cd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段采购汇总" sheetId="2" r:id="R4fc852c88f724d06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现有资产匹配" sheetId="3" r:id="Rbe1f30a8e5bf4f54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待确认项" sheetId="4" r:id="Ra52fe2f2717a40b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM主表" sheetId="1" r:id="R7ebc10d86132402f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段采购汇总" sheetId="2" r:id="R8c32a3244fb044b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现有资产匹配" sheetId="3" r:id="R44c86e25d6d64a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待确认项" sheetId="4" r:id="Ra1b6827880a04017"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +21,7 @@
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -71,8 +71,13 @@
       <x:color rgb="FF203040"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF203040"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -117,6 +122,41 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -176,7 +216,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="109">
+  <x:cellXfs count="181">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -453,6 +493,210 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -464,7 +708,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -474,7 +718,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -484,7 +728,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -494,7 +738,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -504,7 +748,7 @@
         <x:color rgb="FF666666"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF2F2F2"/>
         </x:patternFill>
       </x:fill>
@@ -543,7 +787,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AssetMatchTable" displayName="AssetMatchTable" ref="A5:M62" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AssetMatchTable" displayName="AssetMatchTable" ref="A5:M75" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="资产编号"/>
     <x:tableColumn id="2" name="管理类别"/>
@@ -873,19 +1117,19 @@
       <x:c r="C4" s="17"/>
       <x:c r="D4" s="17" t="n">
         <x:f>COUNTIF(L7:L74,"&gt;0")</x:f>
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E4" s="17"/>
       <x:c r="F4" s="17"/>
       <x:c r="G4" s="17" t="n">
         <x:f>SUM(P7:P74)</x:f>
-        <x:v>1158</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="H4" s="17"/>
       <x:c r="I4" s="17"/>
       <x:c r="J4" s="17" t="n">
         <x:f>COUNTIF(R7:R74,"待选型")</x:f>
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K4" s="17"/>
       <x:c r="L4" s="17"/>
@@ -964,7 +1208,7 @@
         <x:v>备注</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="84" customHeight="1">
       <x:c r="A7" s="40" t="str">
         <x:v>CPI-MECH-001</x:v>
       </x:c>
@@ -993,40 +1237,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J7" s="51" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K7" s="52" t="n">
         <x:f>MAX(0,G7-J7)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L7" s="52" t="n">
         <x:f>MAX(0,H7-J7)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M7" s="52" t="n">
         <x:f>MAX(0,I7-MAX(0,J7-H7))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N7" s="58"/>
-      <x:c r="O7" s="59" t="str">
+      <x:c r="N7" s="58" t="n">
+        <x:v>1145</x:v>
+      </x:c>
+      <x:c r="O7" s="59" t="n">
         <x:f>IF(N7="","",K7*N7)</x:f>
-      </x:c>
-      <x:c r="P7" s="59" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="59" t="n">
         <x:f>IF(N7="","",L7*N7)</x:f>
-      </x:c>
-      <x:c r="Q7" s="59" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" s="59" t="n">
         <x:f>IF(N7="","",M7*N7)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R7" s="40" t="str">
-        <x:v>待选型</x:v>
-      </x:c>
-      <x:c r="S7" s="40"/>
-      <x:c r="T7" s="65"/>
+        <x:v>已有</x:v>
+      </x:c>
+      <x:c r="S7" s="40" t="str">
+        <x:v>ZC-20260818-005</x:v>
+      </x:c>
+      <x:c r="T7" s="65" t="n">
+        <x:v>46252</x:v>
+      </x:c>
       <x:c r="U7" s="40" t="str">
-        <x:v>规格已确认；30 m耐压能力仍需结构校核和水压试验</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>已购外径160×300mm整套密封舱，含亚克力圆管、半球罩、法兰、金属圈、端盖、密封圈、硅脂和配套螺丝；筒体壁厚、接口及30m耐压能力仍需到货验收和水压试验</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="66" customHeight="1">
       <x:c r="A8" s="41" t="str">
         <x:v>CPI-MECH-002</x:v>
       </x:c>
@@ -1085,10 +1338,10 @@
       <x:c r="S8" s="41"/>
       <x:c r="T8" s="66"/>
       <x:c r="U8" s="41" t="str">
-        <x:v>需完成端盖厚度、材料和连接方式校核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+        <x:v>套装已含半球罩和端盖；具体数量、材料、厚度、密封槽及连接方式待到货核验，暂不冲减待购量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="66" customHeight="1">
       <x:c r="A9" s="42" t="str">
         <x:v>CPI-MECH-003</x:v>
       </x:c>
@@ -1147,10 +1400,10 @@
       <x:c r="S9" s="42"/>
       <x:c r="T9" s="67"/>
       <x:c r="U9" s="42" t="str">
-        <x:v>按端盖设计确定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+        <x:v>套装已含法兰、金属圈和配套螺丝；数量、尺寸及锁紧结构待到货核验，暂不冲减待购量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="66" customHeight="1">
       <x:c r="A10" s="41" t="str">
         <x:v>CPI-SEAL-001</x:v>
       </x:c>
@@ -1209,7 +1462,7 @@
       <x:c r="S10" s="41"/>
       <x:c r="T10" s="66"/>
       <x:c r="U10" s="41" t="str">
-        <x:v>密封圈截面、材料和压缩率需按端盖槽确认</x:v>
+        <x:v>套装已含密封圈；数量、截面、材料及压缩率待到货核验，暂不冲减待购量</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1551,7 +1804,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J16" s="53" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K16" s="54" t="n">
         <x:f>MAX(0,G16-J16)</x:f>
@@ -1559,7 +1812,7 @@
       </x:c>
       <x:c r="L16" s="54" t="n">
         <x:f>MAX(0,H16-J16)</x:f>
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M16" s="54" t="n">
         <x:f>MAX(0,I16-MAX(0,J16-H16))</x:f>
@@ -1574,23 +1827,23 @@
       </x:c>
       <x:c r="P16" s="61" t="n">
         <x:f>IF(N16="","",L16*N16)</x:f>
-        <x:v>567</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q16" s="61" t="n">
         <x:f>IF(N16="","",M16*N16)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R16" s="41" t="str">
-        <x:v>部分已有</x:v>
+        <x:v>已有</x:v>
       </x:c>
       <x:c r="S16" s="41" t="str">
-        <x:v>ZC-20260713-009</x:v>
+        <x:v>ZC-20260713-009；ZC-20260818-003</x:v>
       </x:c>
       <x:c r="T16" s="66" t="n">
-        <x:v>46216</x:v>
+        <x:v>46252</x:v>
       </x:c>
       <x:c r="U16" s="41" t="str">
-        <x:v>第一版四推进器；现有1个，需补足3个</x:v>
+        <x:v>第一版四推进器已配齐：原有1个，本次新增3个</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1622,7 +1875,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J17" s="55" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K17" s="54" t="n">
         <x:f>MAX(0,G17-J17)</x:f>
@@ -1630,7 +1883,7 @@
       </x:c>
       <x:c r="L17" s="54" t="n">
         <x:f>MAX(0,H17-J17)</x:f>
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M17" s="54" t="n">
         <x:f>MAX(0,I17-MAX(0,J17-H17))</x:f>
@@ -1645,23 +1898,23 @@
       </x:c>
       <x:c r="P17" s="61" t="n">
         <x:f>IF(N17="","",L17*N17)</x:f>
-        <x:v>285</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q17" s="61" t="n">
         <x:f>IF(N17="","",M17*N17)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R17" s="42" t="str">
-        <x:v>部分已有</x:v>
+        <x:v>已有</x:v>
       </x:c>
       <x:c r="S17" s="42" t="str">
-        <x:v>ZC-20260713-011</x:v>
+        <x:v>ZC-20260713-011；ZC-20260818-004</x:v>
       </x:c>
       <x:c r="T17" s="67" t="n">
-        <x:v>46216</x:v>
+        <x:v>46252</x:v>
       </x:c>
       <x:c r="U17" s="42" t="str">
-        <x:v>每个推进器配置1个电调</x:v>
+        <x:v>第一版4个双向电调已配齐：原有1个，本次新增3个</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -3121,37 +3374,46 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J39" s="55" t="n">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K39" s="54" t="n">
         <x:f>MAX(0,G39-J39)</x:f>
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L39" s="54" t="n">
         <x:f>MAX(0,H39-J39)</x:f>
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M39" s="54" t="n">
         <x:f>MAX(0,I39-MAX(0,J39-H39))</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="N39" s="62"/>
-      <x:c r="O39" s="61" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N39" s="62" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O39" s="61" t="n">
         <x:f>IF(N39="","",K39*N39)</x:f>
-      </x:c>
-      <x:c r="P39" s="61" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P39" s="61" t="n">
         <x:f>IF(N39="","",L39*N39)</x:f>
-      </x:c>
-      <x:c r="Q39" s="61" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q39" s="61" t="n">
         <x:f>IF(N39="","",M39*N39)</x:f>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="R39" s="42" t="str">
-        <x:v>待选型</x:v>
-      </x:c>
-      <x:c r="S39" s="42"/>
-      <x:c r="T39" s="67"/>
+        <x:v>部分已有</x:v>
+      </x:c>
+      <x:c r="S39" s="42" t="str">
+        <x:v>ZC-20260818-002</x:v>
+      </x:c>
+      <x:c r="T39" s="67" t="n">
+        <x:v>46252</x:v>
+      </x:c>
       <x:c r="U39" s="42" t="str">
-        <x:v>当前为建议数量；需按4推进器、2灯、传感器和电源开关逐项复核</x:v>
+        <x:v>本次购M10穿线螺丝9个，第一版需求8个已覆盖并余1个；后续升级仍需按线缆表复核</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3216,7 +3478,7 @@
         <x:v>用于负压检漏和压力测试流程</x:v>
       </x:c>
     </x:row>
-    <x:row r="41">
+    <x:row r="41" ht="66" customHeight="1">
       <x:c r="A41" s="42" t="str">
         <x:v>CPI-SEAL-004</x:v>
       </x:c>
@@ -3275,7 +3537,7 @@
       <x:c r="S41" s="42"/>
       <x:c r="T41" s="67"/>
       <x:c r="U41" s="42" t="str">
-        <x:v>用于密封圈装配维护</x:v>
+        <x:v>套装已含硅脂；包装量及与密封圈材料的相容性待到货核验，暂不冲减待购量</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4185,7 +4447,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J55" s="55" t="n">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K55" s="54" t="n">
         <x:f>MAX(0,G55-J55)</x:f>
@@ -4200,7 +4462,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="N55" s="62" t="n">
-        <x:v>0.2492</x:v>
+        <x:v>0.2588571428571429</x:v>
       </x:c>
       <x:c r="O55" s="61" t="n">
         <x:f>IF(N55="","",K55*N55)</x:f>
@@ -4218,13 +4480,13 @@
         <x:v>已有</x:v>
       </x:c>
       <x:c r="S55" s="42" t="str">
-        <x:v>ZC-20260722-004</x:v>
+        <x:v>ZC-20260722-004；ZC-20260817-004</x:v>
       </x:c>
       <x:c r="T55" s="67" t="n">
-        <x:v>46225</x:v>
+        <x:v>46251</x:v>
       </x:c>
       <x:c r="U55" s="42" t="str">
-        <x:v>板卡安装</x:v>
+        <x:v>板卡安装；现有50支M3×20+3，另购20支M3×20+6，装配前确认螺柱端长度</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -5471,7 +5733,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8882955fe5a64ae7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb62572bc62f4282"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5560,19 +5822,19 @@
       </x:c>
       <x:c r="D5" s="78" t="n">
         <x:f>COUNTIFS('BOM主表'!G7:G74,"&gt;0",'BOM主表'!J7:J74,"&gt;0")</x:f>
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E5" s="78" t="n">
         <x:f>COUNTIF('BOM主表'!K7:K74,"&gt;0")</x:f>
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F5" s="78" t="n">
         <x:f>SUM('BOM主表'!K7:K74)</x:f>
-        <x:v>84</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G5" s="78" t="n">
         <x:f>COUNTIFS('BOM主表'!G7:G74,"&gt;0",'BOM主表'!N7:N74,"&gt;0")</x:f>
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H5" s="81" t="n">
         <x:f>SUM('BOM主表'!O7:O74)</x:f>
@@ -5580,7 +5842,7 @@
       </x:c>
       <x:c r="I5" s="76" t="n">
         <x:f>COUNTIFS('BOM主表'!G7:G74,"&gt;0",'BOM主表'!R7:R74,"待选型")</x:f>
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25.5" customHeight="1">
@@ -5597,27 +5859,27 @@
       </x:c>
       <x:c r="D6" s="79" t="n">
         <x:f>COUNTIFS('BOM主表'!H7:H74,"&gt;0",'BOM主表'!J7:J74,"&gt;0")</x:f>
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E6" s="79" t="n">
         <x:f>COUNTIF('BOM主表'!L7:L74,"&gt;0")</x:f>
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F6" s="79" t="n">
         <x:f>SUM('BOM主表'!L7:L74)</x:f>
-        <x:v>93</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G6" s="79" t="n">
         <x:f>COUNTIFS('BOM主表'!H7:H74,"&gt;0",'BOM主表'!N7:N74,"&gt;0")</x:f>
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H6" s="82" t="n">
         <x:f>SUM('BOM主表'!P7:P74)</x:f>
-        <x:v>1158</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="I6" s="74" t="n">
         <x:f>COUNTIFS('BOM主表'!H7:H74,"&gt;0",'BOM主表'!R7:R74,"待选型")</x:f>
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="25.5" customHeight="1">
@@ -5634,7 +5896,7 @@
       </x:c>
       <x:c r="D7" s="80" t="n">
         <x:f>COUNTIFS('BOM主表'!I7:I74,"&gt;0",'BOM主表'!J7:J74,"&gt;0")</x:f>
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E7" s="80" t="n">
         <x:f>COUNTIF('BOM主表'!M7:M74,"&gt;0")</x:f>
@@ -5642,24 +5904,24 @@
       </x:c>
       <x:c r="F7" s="80" t="n">
         <x:f>SUM('BOM主表'!M7:M74)</x:f>
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G7" s="80" t="n">
         <x:f>COUNTIFS('BOM主表'!I7:I74,"&gt;0",'BOM主表'!N7:N74,"&gt;0")</x:f>
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H7" s="83" t="n">
         <x:f>SUM('BOM主表'!Q7:Q74)</x:f>
-        <x:v>20.78</x:v>
+        <x:v>110.78</x:v>
       </x:c>
       <x:c r="I7" s="77" t="n">
         <x:f>COUNTIFS('BOM主表'!I7:I74,"&gt;0",'BOM主表'!R7:R74,"待选型")</x:f>
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="21" t="str">
-        <x:v>来源核对：采购清单共57类、74件，采购总额4202.81元；资产清单中运费、快递费与打包费未纳入资产。本表只匹配机器人本体与装配耗材。</x:v>
+        <x:v>来源核对：采购清单共71类、103件，采购总额6735.69元；资产清单中运费、快递费与打包费未纳入资产。本表只匹配机器人本体与装配耗材。</x:v>
       </x:c>
       <x:c r="B9" s="21"/>
       <x:c r="C9" s="21"/>
@@ -8058,6 +8320,529 @@
         <x:v>10条合计4.30元</x:v>
       </x:c>
     </x:row>
+    <x:row r="63" ht="42" customHeight="1">
+      <x:c r="A63" s="116" t="str">
+        <x:v>ZC-20260817-001</x:v>
+      </x:c>
+      <x:c r="B63" s="116" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C63" s="116" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D63" s="119" t="str">
+        <x:v>美标特软硅胶线</x:v>
+      </x:c>
+      <x:c r="E63" s="119" t="str">
+        <x:v>28AWG / 黑色 / 10米/卷</x:v>
+      </x:c>
+      <x:c r="F63" s="122" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G63" s="128" t="n">
+        <x:v>8.49</x:v>
+      </x:c>
+      <x:c r="H63" s="128" t="n">
+        <x:v>8.49</x:v>
+      </x:c>
+      <x:c r="I63" s="131" t="n">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="J63" s="116" t="str">
+        <x:v>skygod旗舰店</x:v>
+      </x:c>
+      <x:c r="K63" s="119"/>
+      <x:c r="L63" s="119" t="str">
+        <x:v>待BOM确认</x:v>
+      </x:c>
+      <x:c r="M63" s="119" t="str">
+        <x:v>28AWG仅适合低电流信号/控制线，不替代CPI-POWER-011的12AWG主电源线；是否纳入单台BOM待线缆表确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="42" customHeight="1">
+      <x:c r="A64" s="117" t="str">
+        <x:v>ZC-20260817-002</x:v>
+      </x:c>
+      <x:c r="B64" s="117" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C64" s="117" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D64" s="120" t="str">
+        <x:v>美标特软硅胶线</x:v>
+      </x:c>
+      <x:c r="E64" s="120" t="str">
+        <x:v>28AWG / 红色 / 10米/卷</x:v>
+      </x:c>
+      <x:c r="F64" s="123" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G64" s="129" t="n">
+        <x:v>8.49</x:v>
+      </x:c>
+      <x:c r="H64" s="129" t="n">
+        <x:v>8.49</x:v>
+      </x:c>
+      <x:c r="I64" s="132" t="n">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="J64" s="117" t="str">
+        <x:v>skygod旗舰店</x:v>
+      </x:c>
+      <x:c r="K64" s="120"/>
+      <x:c r="L64" s="120" t="str">
+        <x:v>待BOM确认</x:v>
+      </x:c>
+      <x:c r="M64" s="120" t="str">
+        <x:v>28AWG仅适合低电流信号/控制线，不替代CPI-POWER-011的12AWG主电源线；是否纳入单台BOM待线缆表确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="42" customHeight="1">
+      <x:c r="A65" s="116" t="str">
+        <x:v>ZC-20260817-003</x:v>
+      </x:c>
+      <x:c r="B65" s="116" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C65" s="116" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D65" s="119" t="str">
+        <x:v>XT60母对母延长线</x:v>
+      </x:c>
+      <x:c r="E65" s="119" t="str">
+        <x:v>0.2m / XT60母对母 / 10AWG（5.3mm²）</x:v>
+      </x:c>
+      <x:c r="F65" s="122" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G65" s="128" t="n">
+        <x:v>15.88</x:v>
+      </x:c>
+      <x:c r="H65" s="128" t="n">
+        <x:v>15.88</x:v>
+      </x:c>
+      <x:c r="I65" s="131" t="n">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="J65" s="116" t="str">
+        <x:v>安捷达线束</x:v>
+      </x:c>
+      <x:c r="K65" s="119"/>
+      <x:c r="L65" s="119" t="str">
+        <x:v>待BOM确认</x:v>
+      </x:c>
+      <x:c r="M65" s="119" t="str">
+        <x:v>规格与CPI-POWER-010的XT60公头/12AWG/30cm不同，暂不冲抵其需求；具体用途待电源线缆表确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="42" customHeight="1">
+      <x:c r="A66" s="118" t="str">
+        <x:v>ZC-20260817-004</x:v>
+      </x:c>
+      <x:c r="B66" s="118" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C66" s="118" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D66" s="121" t="str">
+        <x:v>六角铜柱机箱螺丝钉</x:v>
+      </x:c>
+      <x:c r="E66" s="121" t="str">
+        <x:v>M3×20+6 / 20颗</x:v>
+      </x:c>
+      <x:c r="F66" s="124" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G66" s="130" t="n">
+        <x:v>5.66</x:v>
+      </x:c>
+      <x:c r="H66" s="130" t="n">
+        <x:v>5.66</x:v>
+      </x:c>
+      <x:c r="I66" s="133" t="n">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="J66" s="118" t="str">
+        <x:v>固万基官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K66" s="121" t="str">
+        <x:v>CPI-CONS-009</x:v>
+      </x:c>
+      <x:c r="L66" s="121" t="str">
+        <x:v>装配耗材</x:v>
+      </x:c>
+      <x:c r="M66" s="121" t="str">
+        <x:v>与20mm铜柱用途一致；螺柱端为6mm，与既有M3×20+3不同，装配前确认孔深</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="42" customHeight="1">
+      <x:c r="A67" s="138" t="str">
+        <x:v>ZC-20260817-005</x:v>
+      </x:c>
+      <x:c r="B67" s="138" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C67" s="138" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D67" s="139" t="str">
+        <x:v>304不锈钢杯头内六角螺钉</x:v>
+      </x:c>
+      <x:c r="E67" s="139" t="str">
+        <x:v>M3×16 / 100个</x:v>
+      </x:c>
+      <x:c r="F67" s="140" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G67" s="142" t="n">
+        <x:v>3.63</x:v>
+      </x:c>
+      <x:c r="H67" s="142" t="n">
+        <x:v>3.63</x:v>
+      </x:c>
+      <x:c r="I67" s="143" t="n">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="J67" s="138" t="str">
+        <x:v>楚卫旗舰店</x:v>
+      </x:c>
+      <x:c r="K67" s="139"/>
+      <x:c r="L67" s="139" t="str">
+        <x:v>待BOM确认</x:v>
+      </x:c>
+      <x:c r="M67" s="139" t="str">
+        <x:v>M3×16杯头内六角规格未在当前BOM主表列出；是否纳入装配耗材待结构图确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="48" customHeight="1">
+      <x:c r="A68" s="144" t="str">
+        <x:v>ZC-20260818-001</x:v>
+      </x:c>
+      <x:c r="B68" s="144" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C68" s="144" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D68" s="147" t="str">
+        <x:v>M10密封舱实心螺栓</x:v>
+      </x:c>
+      <x:c r="E68" s="147" t="str">
+        <x:v>铝制密封螺丝 / M10</x:v>
+      </x:c>
+      <x:c r="F68" s="150" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G68" s="156" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H68" s="156" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I68" s="159" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J68" s="144" t="str">
+        <x:v>天启ROV97</x:v>
+      </x:c>
+      <x:c r="K68" s="147"/>
+      <x:c r="L68" s="147" t="str">
+        <x:v>待BOM确认</x:v>
+      </x:c>
+      <x:c r="M68" s="147" t="str">
+        <x:v>当前BOM未单列M10密封舱实心螺栓；具体安装位置与数量待密封舱结构图确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="48" customHeight="1">
+      <x:c r="A69" s="145" t="str">
+        <x:v>ZC-20260818-002</x:v>
+      </x:c>
+      <x:c r="B69" s="145" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C69" s="145" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D69" s="148" t="str">
+        <x:v>M10穿线螺丝</x:v>
+      </x:c>
+      <x:c r="E69" s="148" t="str">
+        <x:v>银色 / 不锈钢 / M10</x:v>
+      </x:c>
+      <x:c r="F69" s="151" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G69" s="157" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H69" s="157" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="I69" s="160" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J69" s="145" t="str">
+        <x:v>天启ROV97</x:v>
+      </x:c>
+      <x:c r="K69" s="148" t="str">
+        <x:v>CPI-SEAL-002</x:v>
+      </x:c>
+      <x:c r="L69" s="148" t="str">
+        <x:v>直接使用</x:v>
+      </x:c>
+      <x:c r="M69" s="148" t="str">
+        <x:v>按主穿舱水密接头/电缆穿透件登记；第一版需求8个，本次购9个，余1个备用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="48" customHeight="1">
+      <x:c r="A70" s="144" t="str">
+        <x:v>ZC-20260818-003</x:v>
+      </x:c>
+      <x:c r="B70" s="144" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C70" s="144" t="str">
+        <x:v>可周转资产</x:v>
+      </x:c>
+      <x:c r="D70" s="147" t="str">
+        <x:v>TS60水下推进器</x:v>
+      </x:c>
+      <x:c r="E70" s="147" t="str">
+        <x:v>蓝黑500KV正桨 / 推荐12V使用</x:v>
+      </x:c>
+      <x:c r="F70" s="150" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G70" s="156" t="n">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H70" s="156" t="n">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="I70" s="159" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J70" s="144" t="str">
+        <x:v>天启ROV97</x:v>
+      </x:c>
+      <x:c r="K70" s="147" t="str">
+        <x:v>CPI-PROP-001</x:v>
+      </x:c>
+      <x:c r="L70" s="147" t="str">
+        <x:v>直接使用</x:v>
+      </x:c>
+      <x:c r="M70" s="147" t="str">
+        <x:v>与原有1个合计4个，第一版四推进器需求已配齐</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="48" customHeight="1">
+      <x:c r="A71" s="145" t="str">
+        <x:v>ZC-20260818-004</x:v>
+      </x:c>
+      <x:c r="B71" s="145" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C71" s="145" t="str">
+        <x:v>可周转资产</x:v>
+      </x:c>
+      <x:c r="D71" s="148" t="str">
+        <x:v>35A双向无刷电调</x:v>
+      </x:c>
+      <x:c r="E71" s="148" t="str">
+        <x:v>35A / 双向 / 水下动力</x:v>
+      </x:c>
+      <x:c r="F71" s="151" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G71" s="157" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H71" s="157" t="n">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="I71" s="160" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J71" s="145" t="str">
+        <x:v>天启ROV97</x:v>
+      </x:c>
+      <x:c r="K71" s="148" t="str">
+        <x:v>CPI-PROP-002</x:v>
+      </x:c>
+      <x:c r="L71" s="148" t="str">
+        <x:v>直接使用</x:v>
+      </x:c>
+      <x:c r="M71" s="148" t="str">
+        <x:v>与原有1个合计4个，第一版每推进器1个电调的需求已配齐</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="96" customHeight="1">
+      <x:c r="A72" s="146" t="str">
+        <x:v>ZC-20260818-005</x:v>
+      </x:c>
+      <x:c r="B72" s="146" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C72" s="146" t="str">
+        <x:v>可周转资产</x:v>
+      </x:c>
+      <x:c r="D72" s="149" t="str">
+        <x:v>海目云水下机器人密封舱</x:v>
+      </x:c>
+      <x:c r="E72" s="180" t="str">
+        <x:v>外径160mm×300mm / 亚克力圆管+半球罩+法兰+金属圈+端盖+密封圈+硅脂+配套螺丝</x:v>
+      </x:c>
+      <x:c r="F72" s="152" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G72" s="158" t="n">
+        <x:v>1145</x:v>
+      </x:c>
+      <x:c r="H72" s="158" t="n">
+        <x:v>1145</x:v>
+      </x:c>
+      <x:c r="I72" s="161" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J72" s="146" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="K72" s="180" t="str">
+        <x:v>CPI-MECH-001；CPI-MECH-002；CPI-MECH-003；CPI-SEAL-001；CPI-SEAL-004</x:v>
+      </x:c>
+      <x:c r="L72" s="180" t="str">
+        <x:v>部分使用</x:v>
+      </x:c>
+      <x:c r="M72" s="180" t="str">
+        <x:v>整套含亚克力圆管、半球罩、法兰、金属圈、端盖、密封圈、硅脂和配套螺丝；已确认组件构成，但端盖/压环/密封圈/硅脂的数量与规格待到货核验，因此暂不冲减相关BOM待购量；筒体壁厚、接口及30m耐压能力仍需验收和水压试验</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="48" customHeight="1">
+      <x:c r="A73" s="162" t="str">
+        <x:v>ZC-20260818-006</x:v>
+      </x:c>
+      <x:c r="B73" s="162" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C73" s="162" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D73" s="165" t="str">
+        <x:v>八合一大电流分电板</x:v>
+      </x:c>
+      <x:c r="E73" s="165" t="str">
+        <x:v>输入XT90 / 输出XT60 / 焊好出货</x:v>
+      </x:c>
+      <x:c r="F73" s="168" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G73" s="174" t="n">
+        <x:v>97.5</x:v>
+      </x:c>
+      <x:c r="H73" s="174" t="n">
+        <x:v>97.5</x:v>
+      </x:c>
+      <x:c r="I73" s="177" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J73" s="162" t="str">
+        <x:v>梁小二模型</x:v>
+      </x:c>
+      <x:c r="K73" s="165" t="str">
+        <x:v>CPI-POWER-001</x:v>
+      </x:c>
+      <x:c r="L73" s="165" t="str">
+        <x:v>部分使用</x:v>
+      </x:c>
+      <x:c r="M73" s="165" t="str">
+        <x:v>升级/替代分电板：XT90输入、多路XT60输出；现有一分四分电板已覆盖主BOM，使用前需确认线序、极性和载流能力</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="48" customHeight="1">
+      <x:c r="A74" s="163" t="str">
+        <x:v>ZC-20260818-007</x:v>
+      </x:c>
+      <x:c r="B74" s="163" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C74" s="163" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D74" s="166" t="str">
+        <x:v>XT90H黑色母头带线</x:v>
+      </x:c>
+      <x:c r="E74" s="166" t="str">
+        <x:v>XT90H黑母头 / 8AWG（8.29mm²）/ 红黑线 / 10cm</x:v>
+      </x:c>
+      <x:c r="F74" s="169" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G74" s="175" t="n">
+        <x:v>10.12</x:v>
+      </x:c>
+      <x:c r="H74" s="175" t="n">
+        <x:v>10.12</x:v>
+      </x:c>
+      <x:c r="I74" s="178" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J74" s="163" t="str">
+        <x:v>阳光模型上海DIY（截图店名截断）</x:v>
+      </x:c>
+      <x:c r="K74" s="166" t="str">
+        <x:v>CPI-POWER-001</x:v>
+      </x:c>
+      <x:c r="L74" s="166" t="str">
+        <x:v>部分使用</x:v>
+      </x:c>
+      <x:c r="M74" s="166" t="str">
+        <x:v>八合一分电板输入侧配套线；接入前需确认XT90H公母头、极性及整机供电架构</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="48" customHeight="1">
+      <x:c r="A75" s="164" t="str">
+        <x:v>ZC-20260818-008</x:v>
+      </x:c>
+      <x:c r="B75" s="164" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C75" s="164" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D75" s="167" t="str">
+        <x:v>XT90H黄色公头带线</x:v>
+      </x:c>
+      <x:c r="E75" s="167" t="str">
+        <x:v>XT90H黄公头 / 8AWG（8.29mm²）/ 红黑线 / 10cm</x:v>
+      </x:c>
+      <x:c r="F75" s="170" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G75" s="176" t="n">
+        <x:v>11.11</x:v>
+      </x:c>
+      <x:c r="H75" s="176" t="n">
+        <x:v>11.11</x:v>
+      </x:c>
+      <x:c r="I75" s="179" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J75" s="164" t="str">
+        <x:v>阳光模型上海DIY（截图店名截断）</x:v>
+      </x:c>
+      <x:c r="K75" s="167" t="str">
+        <x:v>CPI-POWER-001</x:v>
+      </x:c>
+      <x:c r="L75" s="167" t="str">
+        <x:v>部分使用</x:v>
+      </x:c>
+      <x:c r="M75" s="167" t="str">
+        <x:v>八合一分电板输入侧配套线；接入前需确认XT90H公母头、极性及整机供电架构</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:M1"/>
@@ -8067,14 +8852,26 @@
     <x:cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="部分使用"/>
     <x:cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="不纳入"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
+  <x:dataValidations count="5">
     <x:dataValidation type="list" sqref="L6:L62">
       <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="L63:L66">
+      <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入,待BOM确认"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="L67">
+      <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入,待BOM确认"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="L68:L72">
+      <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入,待BOM确认"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="L73:L75">
+      <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入,待BOM确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd17c5ffde3e34877"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4217bb2185d34719"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/物资/CavePI水下机器人BOM.xlsx
+++ b/物资/CavePI水下机器人BOM.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM主表" sheetId="1" r:id="R7ebc10d86132402f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段采购汇总" sheetId="2" r:id="R8c32a3244fb044b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现有资产匹配" sheetId="3" r:id="R44c86e25d6d64a4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待确认项" sheetId="4" r:id="Ra1b6827880a04017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM主表" sheetId="1" r:id="R63fdedd3d045498f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段采购汇总" sheetId="2" r:id="Rc8b9e376a7e543b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现有资产匹配" sheetId="3" r:id="R58547dd82ece4faa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待确认项" sheetId="4" r:id="R1b077f399e3e4fc9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -77,7 +77,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="17">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -159,6 +159,16 @@
         <x:fgColor rgb="FFDDEBF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="8">
     <x:border/>
@@ -216,7 +226,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="181">
+  <x:cellXfs count="199">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -697,6 +707,60 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -787,7 +851,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AssetMatchTable" displayName="AssetMatchTable" ref="A5:M75" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AssetMatchTable" displayName="AssetMatchTable" ref="A5:M85" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="资产编号"/>
     <x:tableColumn id="2" name="管理类别"/>
@@ -1117,7 +1181,7 @@
       <x:c r="C4" s="17"/>
       <x:c r="D4" s="17" t="n">
         <x:f>COUNTIF(L7:L74,"&gt;0")</x:f>
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E4" s="17"/>
       <x:c r="F4" s="17"/>
@@ -1129,7 +1193,7 @@
       <x:c r="I4" s="17"/>
       <x:c r="J4" s="17" t="n">
         <x:f>COUNTIF(R7:R74,"待选型")</x:f>
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K4" s="17"/>
       <x:c r="L4" s="17"/>
@@ -2343,7 +2407,7 @@
         <x:v>仅用于调试，不作为第一版续航电池</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
+    <x:row r="24" ht="60" customHeight="1">
       <x:c r="A24" s="41" t="str">
         <x:v>CPI-POWER-007</x:v>
       </x:c>
@@ -2372,7 +2436,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J24" s="53" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K24" s="54" t="n">
         <x:f>MAX(0,G24-J24)</x:f>
@@ -2380,29 +2444,38 @@
       </x:c>
       <x:c r="L24" s="54" t="n">
         <x:f>MAX(0,H24-J24)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M24" s="54" t="n">
         <x:f>MAX(0,I24-MAX(0,J24-H24))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N24" s="60"/>
-      <x:c r="O24" s="61" t="str">
+      <x:c r="N24" s="60" t="n">
+        <x:v>1552</x:v>
+      </x:c>
+      <x:c r="O24" s="61" t="n">
         <x:f>IF(N24="","",K24*N24)</x:f>
-      </x:c>
-      <x:c r="P24" s="61" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P24" s="61" t="n">
         <x:f>IF(N24="","",L24*N24)</x:f>
-      </x:c>
-      <x:c r="Q24" s="61" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q24" s="61" t="n">
         <x:f>IF(N24="","",M24*N24)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R24" s="41" t="str">
-        <x:v>待选型</x:v>
-      </x:c>
-      <x:c r="S24" s="41"/>
-      <x:c r="T24" s="66"/>
+        <x:v>部分已有</x:v>
+      </x:c>
+      <x:c r="S24" s="41" t="str">
+        <x:v>ZC-20260825-003</x:v>
+      </x:c>
+      <x:c r="T24" s="66" t="n">
+        <x:v>46259</x:v>
+      </x:c>
       <x:c r="U24" s="41" t="str">
-        <x:v>按1-2h续航目标，以平均电流、可用放电深度和舱内容积校核</x:v>
+        <x:v>已购4S6P 14.8V 18Ah电池；容量低于建议20–30Ah，尺寸、持续放电能力及1–2h续航仍需实测</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -3540,7 +3613,7 @@
         <x:v>套装已含硅脂；包装量及与密封圈材料的相容性待到货核验，暂不冲减待购量</x:v>
       </x:c>
     </x:row>
-    <x:row r="42">
+    <x:row r="42" ht="60" customHeight="1">
       <x:c r="A42" s="41" t="str">
         <x:v>CPI-SEAL-005</x:v>
       </x:c>
@@ -3569,37 +3642,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J42" s="53" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K42" s="54" t="n">
         <x:f>MAX(0,G42-J42)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L42" s="54" t="n">
         <x:f>MAX(0,H42-J42)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M42" s="54" t="n">
         <x:f>MAX(0,I42-MAX(0,J42-H42))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N42" s="60"/>
-      <x:c r="O42" s="61" t="str">
+      <x:c r="N42" s="60" t="n">
+        <x:v>15.1</x:v>
+      </x:c>
+      <x:c r="O42" s="61" t="n">
         <x:f>IF(N42="","",K42*N42)</x:f>
-      </x:c>
-      <x:c r="P42" s="61" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P42" s="61" t="n">
         <x:f>IF(N42="","",L42*N42)</x:f>
-      </x:c>
-      <x:c r="Q42" s="61" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q42" s="61" t="n">
         <x:f>IF(N42="","",M42*N42)</x:f>
+        <x:v>15.1</x:v>
       </x:c>
       <x:c r="R42" s="41" t="str">
-        <x:v>待选型</x:v>
-      </x:c>
-      <x:c r="S42" s="41"/>
-      <x:c r="T42" s="66"/>
+        <x:v>部分已有</x:v>
+      </x:c>
+      <x:c r="S42" s="41" t="str">
+        <x:v>ZC-20260825-002</x:v>
+      </x:c>
+      <x:c r="T42" s="66" t="n">
+        <x:v>46259</x:v>
+      </x:c>
       <x:c r="U42" s="41" t="str">
-        <x:v>需先做材料相容性和固化工艺试验</x:v>
+        <x:v>已购黑色快干AB环氧树脂胶；作为灌封/粘接候选，需完成长期浸泡、材料相容性及固化工艺试验</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -4773,7 +4855,7 @@
         <x:v>按单台项目领用份额管理</x:v>
       </x:c>
     </x:row>
-    <x:row r="60">
+    <x:row r="60" ht="54" customHeight="1">
       <x:c r="A60" s="41" t="str">
         <x:v>CPI-CONS-014</x:v>
       </x:c>
@@ -4827,12 +4909,16 @@
         <x:f>IF(N60="","",M60*N60)</x:f>
       </x:c>
       <x:c r="R60" s="41" t="str">
-        <x:v>待选型</x:v>
-      </x:c>
-      <x:c r="S60" s="41"/>
-      <x:c r="T60" s="66"/>
+        <x:v>部分已有</x:v>
+      </x:c>
+      <x:c r="S60" s="41" t="str">
+        <x:v>ZC-20260826-006</x:v>
+      </x:c>
+      <x:c r="T60" s="66" t="n">
+        <x:v>46260</x:v>
+      </x:c>
       <x:c r="U60" s="41" t="str">
-        <x:v>舱内线束整理</x:v>
+        <x:v>已购4×150mm黑色尼龙扎带500根；未见线束固定座，暂不冲减套件待购量</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -5733,7 +5819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb62572bc62f4282"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77891a89cb264e0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5822,19 +5908,19 @@
       </x:c>
       <x:c r="D5" s="78" t="n">
         <x:f>COUNTIFS('BOM主表'!G7:G74,"&gt;0",'BOM主表'!J7:J74,"&gt;0")</x:f>
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E5" s="78" t="n">
         <x:f>COUNTIF('BOM主表'!K7:K74,"&gt;0")</x:f>
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F5" s="78" t="n">
         <x:f>SUM('BOM主表'!K7:K74)</x:f>
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G5" s="78" t="n">
         <x:f>COUNTIFS('BOM主表'!G7:G74,"&gt;0",'BOM主表'!N7:N74,"&gt;0")</x:f>
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H5" s="81" t="n">
         <x:f>SUM('BOM主表'!O7:O74)</x:f>
@@ -5842,7 +5928,7 @@
       </x:c>
       <x:c r="I5" s="76" t="n">
         <x:f>COUNTIFS('BOM主表'!G7:G74,"&gt;0",'BOM主表'!R7:R74,"待选型")</x:f>
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25.5" customHeight="1">
@@ -5859,19 +5945,19 @@
       </x:c>
       <x:c r="D6" s="79" t="n">
         <x:f>COUNTIFS('BOM主表'!H7:H74,"&gt;0",'BOM主表'!J7:J74,"&gt;0")</x:f>
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E6" s="79" t="n">
         <x:f>COUNTIF('BOM主表'!L7:L74,"&gt;0")</x:f>
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F6" s="79" t="n">
         <x:f>SUM('BOM主表'!L7:L74)</x:f>
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G6" s="79" t="n">
         <x:f>COUNTIFS('BOM主表'!H7:H74,"&gt;0",'BOM主表'!N7:N74,"&gt;0")</x:f>
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H6" s="82" t="n">
         <x:f>SUM('BOM主表'!P7:P74)</x:f>
@@ -5879,7 +5965,7 @@
       </x:c>
       <x:c r="I6" s="74" t="n">
         <x:f>COUNTIFS('BOM主表'!H7:H74,"&gt;0",'BOM主表'!R7:R74,"待选型")</x:f>
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="25.5" customHeight="1">
@@ -5896,7 +5982,7 @@
       </x:c>
       <x:c r="D7" s="80" t="n">
         <x:f>COUNTIFS('BOM主表'!I7:I74,"&gt;0",'BOM主表'!J7:J74,"&gt;0")</x:f>
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E7" s="80" t="n">
         <x:f>COUNTIF('BOM主表'!M7:M74,"&gt;0")</x:f>
@@ -5908,20 +5994,20 @@
       </x:c>
       <x:c r="G7" s="80" t="n">
         <x:f>COUNTIFS('BOM主表'!I7:I74,"&gt;0",'BOM主表'!N7:N74,"&gt;0")</x:f>
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H7" s="83" t="n">
         <x:f>SUM('BOM主表'!Q7:Q74)</x:f>
-        <x:v>110.78</x:v>
+        <x:v>125.88</x:v>
       </x:c>
       <x:c r="I7" s="77" t="n">
         <x:f>COUNTIFS('BOM主表'!I7:I74,"&gt;0",'BOM主表'!R7:R74,"待选型")</x:f>
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="21" t="str">
-        <x:v>来源核对：采购清单共71类、103件，采购总额6735.69元；资产清单中运费、快递费与打包费未纳入资产。本表只匹配机器人本体与装配耗材。</x:v>
+        <x:v>来源核对：采购清单共81类、113件，采购总额8589.73元；资产清单中运费、快递费与打包费未纳入资产。本表只匹配机器人本体与装配耗材。</x:v>
       </x:c>
       <x:c r="B9" s="21"/>
       <x:c r="C9" s="21"/>
@@ -8843,6 +8929,406 @@
         <x:v>八合一分电板输入侧配套线；接入前需确认XT90H公母头、极性及整机供电架构</x:v>
       </x:c>
     </x:row>
+    <x:row r="76" ht="54" customHeight="1">
+      <x:c r="A76" s="181" t="str">
+        <x:v>ZC-20260825-001</x:v>
+      </x:c>
+      <x:c r="B76" s="181" t="str">
+        <x:v>工具器具</x:v>
+      </x:c>
+      <x:c r="C76" s="181" t="str">
+        <x:v>通用工具</x:v>
+      </x:c>
+      <x:c r="D76" s="184" t="str">
+        <x:v>密封舱气密性测试套装</x:v>
+      </x:c>
+      <x:c r="E76" s="184" t="str">
+        <x:v>真空枪+宝塔气嘴 / 工具箱套装</x:v>
+      </x:c>
+      <x:c r="F76" s="187" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G76" s="193" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H76" s="193" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="I76" s="196" t="n">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="J76" s="181" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="K76" s="184" t="str">
+        <x:v>CPI-SEAL-003</x:v>
+      </x:c>
+      <x:c r="L76" s="184" t="str">
+        <x:v>通用工具不纳入</x:v>
+      </x:c>
+      <x:c r="M76" s="184" t="str">
+        <x:v>用于密封舱负压气密性测试；属于外部测试工具，不替代装机的泄压/抽真空测试阀</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="54" customHeight="1">
+      <x:c r="A77" s="182" t="str">
+        <x:v>ZC-20260825-002</x:v>
+      </x:c>
+      <x:c r="B77" s="182" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C77" s="182" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D77" s="185" t="str">
+        <x:v>黑色快干AB环氧树脂胶</x:v>
+      </x:c>
+      <x:c r="E77" s="185" t="str">
+        <x:v>黑色快干款 / 5分钟初固 / 两支装 / 送工具</x:v>
+      </x:c>
+      <x:c r="F77" s="188" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G77" s="194" t="n">
+        <x:v>15.1</x:v>
+      </x:c>
+      <x:c r="H77" s="194" t="n">
+        <x:v>15.1</x:v>
+      </x:c>
+      <x:c r="I77" s="197" t="n">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="J77" s="182" t="str">
+        <x:v>固万旗舰店</x:v>
+      </x:c>
+      <x:c r="K77" s="185" t="str">
+        <x:v>CPI-SEAL-005</x:v>
+      </x:c>
+      <x:c r="L77" s="185" t="str">
+        <x:v>部分使用</x:v>
+      </x:c>
+      <x:c r="M77" s="185" t="str">
+        <x:v>可作为灌封/粘接候选；水下长期浸泡、线皮与舱体材料相容性及固化工艺仍需试验</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="54" customHeight="1">
+      <x:c r="A78" s="181" t="str">
+        <x:v>ZC-20260825-003</x:v>
+      </x:c>
+      <x:c r="B78" s="181" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C78" s="181" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D78" s="184" t="str">
+        <x:v>4S6P水下机器人锂电池</x:v>
+      </x:c>
+      <x:c r="E78" s="184" t="str">
+        <x:v>14.8V / 18Ah / 4S6P</x:v>
+      </x:c>
+      <x:c r="F78" s="187" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G78" s="193" t="n">
+        <x:v>1552</x:v>
+      </x:c>
+      <x:c r="H78" s="193" t="n">
+        <x:v>1552</x:v>
+      </x:c>
+      <x:c r="I78" s="196" t="n">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="J78" s="181" t="str">
+        <x:v>仙藤电池</x:v>
+      </x:c>
+      <x:c r="K78" s="184" t="str">
+        <x:v>CPI-POWER-007</x:v>
+      </x:c>
+      <x:c r="L78" s="184" t="str">
+        <x:v>部分使用</x:v>
+      </x:c>
+      <x:c r="M78" s="184" t="str">
+        <x:v>4S电压匹配，18Ah低于BOM建议20–30Ah；尺寸、持续放电能力和1–2h续航仍需实测</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="54" customHeight="1">
+      <x:c r="A79" s="182" t="str">
+        <x:v>ZC-20260826-001</x:v>
+      </x:c>
+      <x:c r="B79" s="182" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C79" s="182" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D79" s="185" t="str">
+        <x:v>M2.5 304不锈钢六角螺母</x:v>
+      </x:c>
+      <x:c r="E79" s="185" t="str">
+        <x:v>M2.5 / 100个</x:v>
+      </x:c>
+      <x:c r="F79" s="188" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G79" s="194" t="n">
+        <x:v>2.46</x:v>
+      </x:c>
+      <x:c r="H79" s="194" t="n">
+        <x:v>2.46</x:v>
+      </x:c>
+      <x:c r="I79" s="197" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J79" s="182" t="str">
+        <x:v>金超官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K79" s="185"/>
+      <x:c r="L79" s="185" t="str">
+        <x:v>待BOM确认</x:v>
+      </x:c>
+      <x:c r="M79" s="185" t="str">
+        <x:v>当前BOM仅单列M3紧固件；是否用于法兰、端盖或舱内安装待结构图确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="54" customHeight="1">
+      <x:c r="A80" s="181" t="str">
+        <x:v>ZC-20260826-002</x:v>
+      </x:c>
+      <x:c r="B80" s="181" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C80" s="181" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D80" s="184" t="str">
+        <x:v>M2.5尼龙平垫片</x:v>
+      </x:c>
+      <x:c r="E80" s="184" t="str">
+        <x:v>M2.5×5×1mm / 200个</x:v>
+      </x:c>
+      <x:c r="F80" s="187" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G80" s="193" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H80" s="193" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I80" s="196" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J80" s="181" t="str">
+        <x:v>品诺塑胶垫圈供应商</x:v>
+      </x:c>
+      <x:c r="K80" s="184"/>
+      <x:c r="L80" s="184" t="str">
+        <x:v>待BOM确认</x:v>
+      </x:c>
+      <x:c r="M80" s="184" t="str">
+        <x:v>当前BOM未单列M2.5尼龙垫片；用途、耐压与材料相容性待结构图确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="54" customHeight="1">
+      <x:c r="A81" s="182" t="str">
+        <x:v>ZC-20260826-003</x:v>
+      </x:c>
+      <x:c r="B81" s="182" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C81" s="182" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D81" s="185" t="str">
+        <x:v>M2.5×8 304不锈钢十字圆头机牙螺钉</x:v>
+      </x:c>
+      <x:c r="E81" s="185" t="str">
+        <x:v>M2.5×8 / 200个</x:v>
+      </x:c>
+      <x:c r="F81" s="188" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G81" s="194" t="n">
+        <x:v>5.71</x:v>
+      </x:c>
+      <x:c r="H81" s="194" t="n">
+        <x:v>5.71</x:v>
+      </x:c>
+      <x:c r="I81" s="197" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J81" s="182" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K81" s="185"/>
+      <x:c r="L81" s="185" t="str">
+        <x:v>待BOM确认</x:v>
+      </x:c>
+      <x:c r="M81" s="185" t="str">
+        <x:v>当前BOM未单列M2.5紧固件；装配位置与实际需求量待结构图确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="54" customHeight="1">
+      <x:c r="A82" s="181" t="str">
+        <x:v>ZC-20260826-004</x:v>
+      </x:c>
+      <x:c r="B82" s="181" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C82" s="181" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D82" s="184" t="str">
+        <x:v>M2.5×6 304不锈钢十字圆头机牙螺钉</x:v>
+      </x:c>
+      <x:c r="E82" s="184" t="str">
+        <x:v>M2.5×6 / 200个</x:v>
+      </x:c>
+      <x:c r="F82" s="187" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G82" s="193" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="H82" s="193" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="I82" s="196" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J82" s="181" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K82" s="184"/>
+      <x:c r="L82" s="184" t="str">
+        <x:v>待BOM确认</x:v>
+      </x:c>
+      <x:c r="M82" s="184" t="str">
+        <x:v>当前BOM未单列M2.5紧固件；装配位置与实际需求量待结构图确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="54" customHeight="1">
+      <x:c r="A83" s="182" t="str">
+        <x:v>ZC-20260826-005</x:v>
+      </x:c>
+      <x:c r="B83" s="182" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C83" s="182" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D83" s="185" t="str">
+        <x:v>M2.5×10 304不锈钢十字圆头机牙螺钉</x:v>
+      </x:c>
+      <x:c r="E83" s="185" t="str">
+        <x:v>M2.5×10 / 200个</x:v>
+      </x:c>
+      <x:c r="F83" s="188" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G83" s="194" t="n">
+        <x:v>6.19</x:v>
+      </x:c>
+      <x:c r="H83" s="194" t="n">
+        <x:v>6.19</x:v>
+      </x:c>
+      <x:c r="I83" s="197" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J83" s="182" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K83" s="185"/>
+      <x:c r="L83" s="185" t="str">
+        <x:v>待BOM确认</x:v>
+      </x:c>
+      <x:c r="M83" s="185" t="str">
+        <x:v>当前BOM未单列M2.5紧固件；装配位置与实际需求量待结构图确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="54" customHeight="1">
+      <x:c r="A84" s="181" t="str">
+        <x:v>ZC-20260826-006</x:v>
+      </x:c>
+      <x:c r="B84" s="181" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C84" s="181" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D84" s="184" t="str">
+        <x:v>黑色自锁式尼龙扎带</x:v>
+      </x:c>
+      <x:c r="E84" s="184" t="str">
+        <x:v>4×150mm / 黑色 / 500根</x:v>
+      </x:c>
+      <x:c r="F84" s="187" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G84" s="193" t="n">
+        <x:v>17.39</x:v>
+      </x:c>
+      <x:c r="H84" s="193" t="n">
+        <x:v>17.39</x:v>
+      </x:c>
+      <x:c r="I84" s="196" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J84" s="181" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K84" s="184" t="str">
+        <x:v>CPI-CONS-014</x:v>
+      </x:c>
+      <x:c r="L84" s="184" t="str">
+        <x:v>部分使用</x:v>
+      </x:c>
+      <x:c r="M84" s="184" t="str">
+        <x:v>已购扎带，未见配套线束固定座；耐潮与老化性能待装配验证，暂不冲减该套件待购量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="54" customHeight="1">
+      <x:c r="A85" s="183" t="str">
+        <x:v>ZC-20260826-007</x:v>
+      </x:c>
+      <x:c r="B85" s="183" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C85" s="183" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D85" s="186" t="str">
+        <x:v>M3×20 304不锈钢杯头内六角螺钉</x:v>
+      </x:c>
+      <x:c r="E85" s="186" t="str">
+        <x:v>M3×20 / 50个</x:v>
+      </x:c>
+      <x:c r="F85" s="189" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G85" s="195" t="n">
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c r="H85" s="195" t="n">
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c r="I85" s="198" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J85" s="183" t="str">
+        <x:v>资鑫旗舰店</x:v>
+      </x:c>
+      <x:c r="K85" s="186" t="str">
+        <x:v>CPI-CONS-004</x:v>
+      </x:c>
+      <x:c r="L85" s="186" t="str">
+        <x:v>部分使用</x:v>
+      </x:c>
+      <x:c r="M85" s="186" t="str">
+        <x:v>长度与BOM一致但头型为杯头内六角；原有M3×20十字圆头库存已覆盖需求，本批作替代/备件</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:M1"/>
@@ -8852,7 +9338,7 @@
     <x:cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="部分使用"/>
     <x:cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="不纳入"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="5">
+  <x:dataValidations count="6">
     <x:dataValidation type="list" sqref="L6:L62">
       <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入"</x:formula1>
     </x:dataValidation>
@@ -8868,10 +9354,13 @@
     <x:dataValidation type="list" sqref="L73:L75">
       <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入,待BOM确认"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="L76:L85">
+      <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入,待BOM确认"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4217bb2185d34719"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3451cc577b54ad8"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/物资/CavePI水下机器人BOM.xlsx
+++ b/物资/CavePI水下机器人BOM.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM主表" sheetId="1" r:id="R63fdedd3d045498f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段采购汇总" sheetId="2" r:id="Rc8b9e376a7e543b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现有资产匹配" sheetId="3" r:id="R58547dd82ece4faa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待确认项" sheetId="4" r:id="R1b077f399e3e4fc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM主表" sheetId="1" r:id="Re18919c7680040e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段采购汇总" sheetId="2" r:id="Rfe6c5d4d793743b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现有资产匹配" sheetId="3" r:id="R5fd1311a74d643be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待确认项" sheetId="4" r:id="R5c41710658fa4ae3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -77,7 +77,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="19">
+  <x:fills count="21">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -169,6 +169,16 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="8">
     <x:border/>
@@ -226,7 +236,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="199">
+  <x:cellXfs count="217">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -760,6 +770,60 @@
       <x:alignment horizontal="center" vertical="center" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="9" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
@@ -851,7 +915,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AssetMatchTable" displayName="AssetMatchTable" ref="A5:M85" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AssetMatchTable" displayName="AssetMatchTable" ref="A5:M92" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="资产编号"/>
     <x:tableColumn id="2" name="管理类别"/>
@@ -1181,19 +1245,19 @@
       <x:c r="C4" s="17"/>
       <x:c r="D4" s="17" t="n">
         <x:f>COUNTIF(L7:L74,"&gt;0")</x:f>
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E4" s="17"/>
       <x:c r="F4" s="17"/>
       <x:c r="G4" s="17" t="n">
         <x:f>SUM(P7:P74)</x:f>
-        <x:v>306</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H4" s="17"/>
       <x:c r="I4" s="17"/>
       <x:c r="J4" s="17" t="n">
         <x:f>COUNTIF(R7:R74,"待选型")</x:f>
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="K4" s="17"/>
       <x:c r="L4" s="17"/>
@@ -1777,7 +1841,7 @@
         <x:v>需在整机称重后校核体积与布置</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="62" customHeight="1">
       <x:c r="A15" s="42" t="str">
         <x:v>CPI-MECH-008</x:v>
       </x:c>
@@ -1833,10 +1897,14 @@
       <x:c r="R15" s="42" t="str">
         <x:v>待选型</x:v>
       </x:c>
-      <x:c r="S15" s="42"/>
-      <x:c r="T15" s="67"/>
+      <x:c r="S15" s="42" t="str">
+        <x:v>ZC-20260828-003</x:v>
+      </x:c>
+      <x:c r="T15" s="67" t="n">
+        <x:v>46262</x:v>
+      </x:c>
       <x:c r="U15" s="42" t="str">
-        <x:v>用于静态姿态与浮心重心调节</x:v>
+        <x:v>已购5块×约200g纯铅配重；可移动安装结构、表面防腐与整机配平尚未确认，暂不冲减待购量</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -3347,7 +3415,7 @@
         <x:v>第一版基础测距；后续声呐升级不覆盖此件</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
+    <x:row r="38" ht="62" customHeight="1">
       <x:c r="A38" s="41" t="str">
         <x:v>CPI-LIGHT-001</x:v>
       </x:c>
@@ -3376,7 +3444,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J38" s="53" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K38" s="54" t="n">
         <x:f>MAX(0,G38-J38)</x:f>
@@ -3384,14 +3452,14 @@
       </x:c>
       <x:c r="L38" s="54" t="n">
         <x:f>MAX(0,H38-J38)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M38" s="54" t="n">
         <x:f>MAX(0,I38-MAX(0,J38-H38))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N38" s="60" t="n">
-        <x:v>306</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="O38" s="61" t="n">
         <x:f>IF(N38="","",K38*N38)</x:f>
@@ -3399,23 +3467,23 @@
       </x:c>
       <x:c r="P38" s="61" t="n">
         <x:f>IF(N38="","",L38*N38)</x:f>
-        <x:v>306</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q38" s="61" t="n">
         <x:f>IF(N38="","",M38*N38)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R38" s="41" t="str">
-        <x:v>部分已有</x:v>
+        <x:v>已有</x:v>
       </x:c>
       <x:c r="S38" s="41" t="str">
-        <x:v>ZC-20260729-002</x:v>
+        <x:v>ZC-20260729-002；ZC-20260828-005</x:v>
       </x:c>
       <x:c r="T38" s="66" t="n">
-        <x:v>46232</x:v>
+        <x:v>46262</x:v>
       </x:c>
       <x:c r="U38" s="41" t="str">
-        <x:v>第一版2盏，现有1盏</x:v>
+        <x:v>第一版两盏探照灯已配齐：原有1盏，本次新增1盏；新增规格为6500K、ArduSub PWM、100°光束角，电压与水密性待实测</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -3580,40 +3648,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J41" s="55" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K41" s="54" t="n">
         <x:f>MAX(0,G41-J41)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L41" s="54" t="n">
         <x:f>MAX(0,H41-J41)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M41" s="54" t="n">
         <x:f>MAX(0,I41-MAX(0,J41-H41))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N41" s="62"/>
-      <x:c r="O41" s="61" t="str">
+      <x:c r="N41" s="62" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="O41" s="61" t="n">
         <x:f>IF(N41="","",K41*N41)</x:f>
-      </x:c>
-      <x:c r="P41" s="61" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P41" s="61" t="n">
         <x:f>IF(N41="","",L41*N41)</x:f>
-      </x:c>
-      <x:c r="Q41" s="61" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q41" s="61" t="n">
         <x:f>IF(N41="","",M41*N41)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R41" s="42" t="str">
-        <x:v>待选型</x:v>
-      </x:c>
-      <x:c r="S41" s="42"/>
-      <x:c r="T41" s="67"/>
+        <x:v>已有</x:v>
+      </x:c>
+      <x:c r="S41" s="42" t="str">
+        <x:v>ZC-20260828-001</x:v>
+      </x:c>
+      <x:c r="T41" s="67" t="n">
+        <x:v>46262</x:v>
+      </x:c>
       <x:c r="U41" s="42" t="str">
-        <x:v>套装已含硅脂；包装量及与密封圈材料的相容性待到货核验，暂不冲减待购量</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="60" customHeight="1">
+        <x:v>已购ROV专用防水密封硅脂；数量覆盖第一版，但与实际O形圈材料的相容性仍需到货核验</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="66" customHeight="1">
       <x:c r="A42" s="41" t="str">
         <x:v>CPI-SEAL-005</x:v>
       </x:c>
@@ -3642,7 +3719,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J42" s="53" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K42" s="54" t="n">
         <x:f>MAX(0,G42-J42)</x:f>
@@ -3654,10 +3731,10 @@
       </x:c>
       <x:c r="M42" s="54" t="n">
         <x:f>MAX(0,I42-MAX(0,J42-H42))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N42" s="60" t="n">
-        <x:v>15.1</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="O42" s="61" t="n">
         <x:f>IF(N42="","",K42*N42)</x:f>
@@ -3669,19 +3746,19 @@
       </x:c>
       <x:c r="Q42" s="61" t="n">
         <x:f>IF(N42="","",M42*N42)</x:f>
-        <x:v>15.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R42" s="41" t="str">
-        <x:v>部分已有</x:v>
+        <x:v>已有</x:v>
       </x:c>
       <x:c r="S42" s="41" t="str">
-        <x:v>ZC-20260825-002</x:v>
+        <x:v>ZC-20260825-002；ZC-20260828-002</x:v>
       </x:c>
       <x:c r="T42" s="66" t="n">
-        <x:v>46259</x:v>
+        <x:v>46262</x:v>
       </x:c>
       <x:c r="U42" s="41" t="str">
-        <x:v>已购黑色快干AB环氧树脂胶；作为灌封/粘接候选，需完成长期浸泡、材料相容性及固化工艺试验</x:v>
+        <x:v>已有黑色快干AB环氧胶与专用穿线密封胶各1份，覆盖第一版及升级阶段数量；仍需完成长期浸泡、材料相容性及固化工艺试验</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -4784,7 +4861,7 @@
         <x:v>仅作辅助绝缘，不作为耐压舱主密封</x:v>
       </x:c>
     </x:row>
-    <x:row r="59">
+    <x:row r="59" ht="62" customHeight="1">
       <x:c r="A59" s="42" t="str">
         <x:v>CPI-CONS-013</x:v>
       </x:c>
@@ -4846,13 +4923,13 @@
         <x:v>部分已有</x:v>
       </x:c>
       <x:c r="S59" s="42" t="str">
-        <x:v>ZC-20260713-001</x:v>
+        <x:v>ZC-20260713-001；ZC-20260830-001</x:v>
       </x:c>
       <x:c r="T59" s="67" t="n">
-        <x:v>46216</x:v>
+        <x:v>46264</x:v>
       </x:c>
       <x:c r="U59" s="42" t="str">
-        <x:v>按单台项目领用份额管理</x:v>
+        <x:v>原有1份无铅低温锡丝；本次新增2卷63%含锡焊丝，可用于调试，但不等同无铅规格，暂不增加BOM合规可用数量</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="54" customHeight="1">
@@ -5819,7 +5896,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77891a89cb264e0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05ce52bbf35c422f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5908,19 +5985,19 @@
       </x:c>
       <x:c r="D5" s="78" t="n">
         <x:f>COUNTIFS('BOM主表'!G7:G74,"&gt;0",'BOM主表'!J7:J74,"&gt;0")</x:f>
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E5" s="78" t="n">
         <x:f>COUNTIF('BOM主表'!K7:K74,"&gt;0")</x:f>
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F5" s="78" t="n">
         <x:f>SUM('BOM主表'!K7:K74)</x:f>
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G5" s="78" t="n">
         <x:f>COUNTIFS('BOM主表'!G7:G74,"&gt;0",'BOM主表'!N7:N74,"&gt;0")</x:f>
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H5" s="81" t="n">
         <x:f>SUM('BOM主表'!O7:O74)</x:f>
@@ -5928,7 +6005,7 @@
       </x:c>
       <x:c r="I5" s="76" t="n">
         <x:f>COUNTIFS('BOM主表'!G7:G74,"&gt;0",'BOM主表'!R7:R74,"待选型")</x:f>
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25.5" customHeight="1">
@@ -5945,27 +6022,27 @@
       </x:c>
       <x:c r="D6" s="79" t="n">
         <x:f>COUNTIFS('BOM主表'!H7:H74,"&gt;0",'BOM主表'!J7:J74,"&gt;0")</x:f>
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E6" s="79" t="n">
         <x:f>COUNTIF('BOM主表'!L7:L74,"&gt;0")</x:f>
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F6" s="79" t="n">
         <x:f>SUM('BOM主表'!L7:L74)</x:f>
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G6" s="79" t="n">
         <x:f>COUNTIFS('BOM主表'!H7:H74,"&gt;0",'BOM主表'!N7:N74,"&gt;0")</x:f>
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H6" s="82" t="n">
         <x:f>SUM('BOM主表'!P7:P74)</x:f>
-        <x:v>306</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="74" t="n">
         <x:f>COUNTIFS('BOM主表'!H7:H74,"&gt;0",'BOM主表'!R7:R74,"待选型")</x:f>
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="25.5" customHeight="1">
@@ -5986,11 +6063,11 @@
       </x:c>
       <x:c r="E7" s="80" t="n">
         <x:f>COUNTIF('BOM主表'!M7:M74,"&gt;0")</x:f>
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F7" s="80" t="n">
         <x:f>SUM('BOM主表'!M7:M74)</x:f>
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G7" s="80" t="n">
         <x:f>COUNTIFS('BOM主表'!I7:I74,"&gt;0",'BOM主表'!N7:N74,"&gt;0")</x:f>
@@ -5998,7 +6075,7 @@
       </x:c>
       <x:c r="H7" s="83" t="n">
         <x:f>SUM('BOM主表'!Q7:Q74)</x:f>
-        <x:v>125.88</x:v>
+        <x:v>110.78</x:v>
       </x:c>
       <x:c r="I7" s="77" t="n">
         <x:f>COUNTIFS('BOM主表'!I7:I74,"&gt;0",'BOM主表'!R7:R74,"待选型")</x:f>
@@ -6007,7 +6084,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="21" t="str">
-        <x:v>来源核对：采购清单共81类、113件，采购总额8589.73元；资产清单中运费、快递费与打包费未纳入资产。本表只匹配机器人本体与装配耗材。</x:v>
+        <x:v>来源核对：采购清单共90类、127件，采购总额9231.69元；资产清单中运费、快递费与打包费未纳入资产。本表只匹配机器人本体与装配耗材。</x:v>
       </x:c>
       <x:c r="B9" s="21"/>
       <x:c r="C9" s="21"/>
@@ -9329,6 +9406,291 @@
         <x:v>长度与BOM一致但头型为杯头内六角；原有M3×20十字圆头库存已覆盖需求，本批作替代/备件</x:v>
       </x:c>
     </x:row>
+    <x:row r="86" ht="58" customHeight="1">
+      <x:c r="A86" s="199" t="str">
+        <x:v>ZC-20260828-001</x:v>
+      </x:c>
+      <x:c r="B86" s="199" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C86" s="199" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D86" s="202" t="str">
+        <x:v>ROV专用防水密封硅脂</x:v>
+      </x:c>
+      <x:c r="E86" s="202" t="str">
+        <x:v>水下密封专用硅脂</x:v>
+      </x:c>
+      <x:c r="F86" s="205" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G86" s="211" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H86" s="211" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I86" s="214" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J86" s="199" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="K86" s="202" t="str">
+        <x:v>CPI-SEAL-004</x:v>
+      </x:c>
+      <x:c r="L86" s="202" t="str">
+        <x:v>直接使用</x:v>
+      </x:c>
+      <x:c r="M86" s="202" t="str">
+        <x:v>与O形圈硅脂直接匹配；到货后仍需核对密封圈材料相容性</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="58" customHeight="1">
+      <x:c r="A87" s="200" t="str">
+        <x:v>ZC-20260828-002</x:v>
+      </x:c>
+      <x:c r="B87" s="200" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C87" s="200" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D87" s="203" t="str">
+        <x:v>水下机器人穿线密封胶</x:v>
+      </x:c>
+      <x:c r="E87" s="203" t="str">
+        <x:v>400米耐压密封胶 / 赠推杆和5个胶管</x:v>
+      </x:c>
+      <x:c r="F87" s="206" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G87" s="212" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H87" s="212" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="I87" s="215" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J87" s="200" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="K87" s="203" t="str">
+        <x:v>CPI-SEAL-005</x:v>
+      </x:c>
+      <x:c r="L87" s="203" t="str">
+        <x:v>直接使用</x:v>
+      </x:c>
+      <x:c r="M87" s="203" t="str">
+        <x:v>专用穿线密封胶匹配灵敏性较高；商家耐压宣称及材料相容性需试验核验</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="58" customHeight="1">
+      <x:c r="A88" s="199" t="str">
+        <x:v>ZC-20260828-003</x:v>
+      </x:c>
+      <x:c r="B88" s="199" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C88" s="199" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D88" s="202" t="str">
+        <x:v>ROV纯铅配重块</x:v>
+      </x:c>
+      <x:c r="E88" s="202" t="str">
+        <x:v>约200g/块</x:v>
+      </x:c>
+      <x:c r="F88" s="205" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G88" s="211" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H88" s="211" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="I88" s="214" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J88" s="199" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="K88" s="202" t="str">
+        <x:v>CPI-MECH-008</x:v>
+      </x:c>
+      <x:c r="L88" s="202" t="str">
+        <x:v>部分使用</x:v>
+      </x:c>
+      <x:c r="M88" s="202" t="str">
+        <x:v>已购5块、合计约1kg；缺少可移动安装结构与防腐处理说明，暂不冲减配重组件待购量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="58" customHeight="1">
+      <x:c r="A89" s="200" t="str">
+        <x:v>ZC-20260828-004</x:v>
+      </x:c>
+      <x:c r="B89" s="200" t="str">
+        <x:v>工具器具</x:v>
+      </x:c>
+      <x:c r="C89" s="200" t="str">
+        <x:v>通用工具</x:v>
+      </x:c>
+      <x:c r="D89" s="203" t="str">
+        <x:v>1:1 AB胶枪</x:v>
+      </x:c>
+      <x:c r="E89" s="203" t="str">
+        <x:v>AB胶枪 / 1比1</x:v>
+      </x:c>
+      <x:c r="F89" s="206" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G89" s="212" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H89" s="212" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I89" s="215" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J89" s="200" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="K89" s="203" t="str">
+        <x:v>CPI-SEAL-005</x:v>
+      </x:c>
+      <x:c r="L89" s="203" t="str">
+        <x:v>通用工具不纳入</x:v>
+      </x:c>
+      <x:c r="M89" s="203" t="str">
+        <x:v>用于密封胶施工；属外部装配工具，不计入机器人本体BOM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="58" customHeight="1">
+      <x:c r="A90" s="199" t="str">
+        <x:v>ZC-20260828-005</x:v>
+      </x:c>
+      <x:c r="B90" s="199" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C90" s="199" t="str">
+        <x:v>可周转资产</x:v>
+      </x:c>
+      <x:c r="D90" s="202" t="str">
+        <x:v>水下机器人ROV探照灯</x:v>
+      </x:c>
+      <x:c r="E90" s="202" t="str">
+        <x:v>6500K / ArduSub脉宽控制 / 100°光束角</x:v>
+      </x:c>
+      <x:c r="F90" s="205" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G90" s="211" t="n">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="H90" s="211" t="n">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="I90" s="214" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J90" s="199" t="str">
+        <x:v>EXOCEAN拓洲智能</x:v>
+      </x:c>
+      <x:c r="K90" s="202" t="str">
+        <x:v>CPI-LIGHT-001</x:v>
+      </x:c>
+      <x:c r="L90" s="202" t="str">
+        <x:v>直接使用</x:v>
+      </x:c>
+      <x:c r="M90" s="202" t="str">
+        <x:v>与现有同类探照灯合计两盏，覆盖第一版需求；电压、PWM及密封性需到货测试</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="58" customHeight="1">
+      <x:c r="A91" s="200" t="str">
+        <x:v>ZC-20260828-006</x:v>
+      </x:c>
+      <x:c r="B91" s="200" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C91" s="200" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D91" s="203" t="str">
+        <x:v>M5×16 304不锈钢杯头内六角螺钉</x:v>
+      </x:c>
+      <x:c r="E91" s="203" t="str">
+        <x:v>M5×16 / 50个</x:v>
+      </x:c>
+      <x:c r="F91" s="206" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G91" s="212" t="n">
+        <x:v>5.36</x:v>
+      </x:c>
+      <x:c r="H91" s="212" t="n">
+        <x:v>5.36</x:v>
+      </x:c>
+      <x:c r="I91" s="215" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J91" s="200" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K91" s="203"/>
+      <x:c r="L91" s="203" t="str">
+        <x:v>待BOM确认</x:v>
+      </x:c>
+      <x:c r="M91" s="203" t="str">
+        <x:v>当前BOM主要单列M3紧固件；M5×16的安装位置和需求量待结构图确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="58" customHeight="1">
+      <x:c r="A92" s="201" t="str">
+        <x:v>ZC-20260830-001</x:v>
+      </x:c>
+      <x:c r="B92" s="201" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C92" s="201" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D92" s="204" t="str">
+        <x:v>绿林高纯度焊锡丝</x:v>
+      </x:c>
+      <x:c r="E92" s="204" t="str">
+        <x:v>锡含量63% / 0.8mm / 50g / 自带松香</x:v>
+      </x:c>
+      <x:c r="F92" s="207" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G92" s="213" t="n">
+        <x:v>15.8</x:v>
+      </x:c>
+      <x:c r="H92" s="213" t="n">
+        <x:v>31.6</x:v>
+      </x:c>
+      <x:c r="I92" s="216" t="n">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="J92" s="201" t="str">
+        <x:v>绿林官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K92" s="204" t="str">
+        <x:v>CPI-CONS-013</x:v>
+      </x:c>
+      <x:c r="L92" s="204" t="str">
+        <x:v>部分使用</x:v>
+      </x:c>
+      <x:c r="M92" s="204" t="str">
+        <x:v>新购为63%含锡焊丝，不等同BOM要求的无铅低温锡丝；可作调试用料，暂不增加合规库存数</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:M1"/>
@@ -9338,7 +9700,7 @@
     <x:cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="部分使用"/>
     <x:cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="不纳入"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="6">
+  <x:dataValidations count="7">
     <x:dataValidation type="list" sqref="L6:L62">
       <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入"</x:formula1>
     </x:dataValidation>
@@ -9357,10 +9719,13 @@
     <x:dataValidation type="list" sqref="L76:L85">
       <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入,待BOM确认"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="L86:L92">
+      <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入,待BOM确认"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3451cc577b54ad8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27b4fcec68e54ef9"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/物资/CavePI水下机器人BOM.xlsx
+++ b/物资/CavePI水下机器人BOM.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM主表" sheetId="1" r:id="Re18919c7680040e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段采购汇总" sheetId="2" r:id="Rfe6c5d4d793743b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现有资产匹配" sheetId="3" r:id="R5fd1311a74d643be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待确认项" sheetId="4" r:id="R5c41710658fa4ae3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM主表" sheetId="1" r:id="R513a03ac04bd430f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段采购汇总" sheetId="2" r:id="R7eb00fd309794bfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现有资产匹配" sheetId="3" r:id="R4d7a01881691476f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待确认项" sheetId="4" r:id="R1234a2b479e54d6d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,10 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="#,##0.##"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="203" formatCode="#,##0.000"/>
   </x:numFmts>
   <x:fonts count="10">
     <x:font>
@@ -77,7 +78,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="21">
+  <x:fills count="25">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -179,6 +180,26 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="8">
     <x:border/>
@@ -236,7 +257,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="217">
+  <x:cellXfs count="264">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -825,6 +846,147 @@
     </x:xf>
     <x:xf numFmtId="202" fontId="9" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="9" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -915,7 +1077,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AssetMatchTable" displayName="AssetMatchTable" ref="A5:M92" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AssetMatchTable" displayName="AssetMatchTable" ref="A5:M101" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="资产编号"/>
     <x:tableColumn id="2" name="管理类别"/>
@@ -5896,7 +6058,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05ce52bbf35c422f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f2c4797a70946b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6084,7 +6246,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="21" t="str">
-        <x:v>来源核对：采购清单共90类、127件，采购总额9231.69元；资产清单中运费、快递费与打包费未纳入资产。本表只匹配机器人本体与装配耗材。</x:v>
+        <x:v>来源核对：采购清单共100类、141件，采购总额9402.88元；资产清单中运费、快递费与打包费未纳入资产。本表只匹配机器人本体与装配耗材。</x:v>
       </x:c>
       <x:c r="B9" s="21"/>
       <x:c r="C9" s="21"/>
@@ -9691,6 +9853,363 @@
         <x:v>新购为63%含锡焊丝，不等同BOM要求的无铅低温锡丝；可作调试用料，暂不增加合规库存数</x:v>
       </x:c>
     </x:row>
+    <x:row r="93" ht="58" customHeight="1">
+      <x:c r="A93" s="245" t="str">
+        <x:v>ZC-20260901-001</x:v>
+      </x:c>
+      <x:c r="B93" s="245" t="str">
+        <x:v>工具器具</x:v>
+      </x:c>
+      <x:c r="C93" s="245" t="str">
+        <x:v>可周转资产</x:v>
+      </x:c>
+      <x:c r="D93" s="257" t="str">
+        <x:v>15件套充电式电动螺丝刀</x:v>
+      </x:c>
+      <x:c r="E93" s="257" t="str">
+        <x:v>15件套 / 充电式 / 手持电钻螺丝刀</x:v>
+      </x:c>
+      <x:c r="F93" s="246" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G93" s="247" t="n">
+        <x:v>27.84</x:v>
+      </x:c>
+      <x:c r="H93" s="247" t="n">
+        <x:v>27.84</x:v>
+      </x:c>
+      <x:c r="I93" s="248" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="J93" s="245" t="str">
+        <x:v>鲸选坐标超市（西丽店）</x:v>
+      </x:c>
+      <x:c r="K93" s="257"/>
+      <x:c r="L93" s="257" t="str">
+        <x:v>通用工具不纳入</x:v>
+      </x:c>
+      <x:c r="M93" s="257" t="str">
+        <x:v>用于外部装配和维护，属于可周转工具，不计入单台机器人本体BOM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="58" customHeight="1">
+      <x:c r="A94" s="249" t="str">
+        <x:v>ZC-20260901-002</x:v>
+      </x:c>
+      <x:c r="B94" s="249" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C94" s="249" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D94" s="258" t="str">
+        <x:v>75%酒精消毒湿巾</x:v>
+      </x:c>
+      <x:c r="E94" s="258" t="str">
+        <x:v>带盖大包 / 75%酒精</x:v>
+      </x:c>
+      <x:c r="F94" s="250" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G94" s="251" t="n">
+        <x:v>5.97</x:v>
+      </x:c>
+      <x:c r="H94" s="251" t="n">
+        <x:v>5.97</x:v>
+      </x:c>
+      <x:c r="I94" s="252" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="J94" s="249" t="str">
+        <x:v>鲸选坐标超市（西丽店）</x:v>
+      </x:c>
+      <x:c r="K94" s="258"/>
+      <x:c r="L94" s="258" t="str">
+        <x:v>非本体采购不纳入</x:v>
+      </x:c>
+      <x:c r="M94" s="258" t="str">
+        <x:v>用于作业清洁和消毒，不安装在机器人本体，不计入单台机器人BOM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="58" customHeight="1">
+      <x:c r="A95" s="245" t="str">
+        <x:v>ZC-20260901-003</x:v>
+      </x:c>
+      <x:c r="B95" s="245" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C95" s="245" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D95" s="257" t="str">
+        <x:v>公牛PVC电工绝缘胶带</x:v>
+      </x:c>
+      <x:c r="E95" s="257" t="str">
+        <x:v>黑色 / 9米/卷 / 阻燃耐低温</x:v>
+      </x:c>
+      <x:c r="F95" s="246" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G95" s="247" t="n">
+        <x:v>3.02</x:v>
+      </x:c>
+      <x:c r="H95" s="247" t="n">
+        <x:v>3.02</x:v>
+      </x:c>
+      <x:c r="I95" s="248" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="J95" s="245" t="str">
+        <x:v>鲸选坐标超市（西丽店）</x:v>
+      </x:c>
+      <x:c r="K95" s="257" t="str">
+        <x:v>CPI-CONS-012</x:v>
+      </x:c>
+      <x:c r="L95" s="257" t="str">
+        <x:v>装配耗材</x:v>
+      </x:c>
+      <x:c r="M95" s="257" t="str">
+        <x:v>作为辅助绝缘和线束整理耗材；现有同类已覆盖主BOM需求，不改变需求数量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="58" customHeight="1">
+      <x:c r="A96" s="249" t="str">
+        <x:v>ZC-20260901-004</x:v>
+      </x:c>
+      <x:c r="B96" s="249" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C96" s="249" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D96" s="258" t="str">
+        <x:v>鹰牌水磨砂纸</x:v>
+      </x:c>
+      <x:c r="E96" s="258" t="str">
+        <x:v>150目</x:v>
+      </x:c>
+      <x:c r="F96" s="250" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G96" s="263" t="n">
+        <x:v>1.194</x:v>
+      </x:c>
+      <x:c r="H96" s="251" t="n">
+        <x:v>5.97</x:v>
+      </x:c>
+      <x:c r="I96" s="252" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="J96" s="249" t="str">
+        <x:v>鲸选坐标超市（西丽店）</x:v>
+      </x:c>
+      <x:c r="K96" s="258"/>
+      <x:c r="L96" s="258" t="str">
+        <x:v>装配耗材</x:v>
+      </x:c>
+      <x:c r="M96" s="258" t="str">
+        <x:v>用于表面打磨和装配前处理；当前BOM未单列该耗材，不改变主BOM需求</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="58" customHeight="1">
+      <x:c r="A97" s="253" t="str">
+        <x:v>ZC-20260902-001</x:v>
+      </x:c>
+      <x:c r="B97" s="253" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C97" s="253" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D97" s="259" t="str">
+        <x:v>XT60并联转接头</x:v>
+      </x:c>
+      <x:c r="E97" s="259" t="str">
+        <x:v>XT60 两母一公</x:v>
+      </x:c>
+      <x:c r="F97" s="254" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G97" s="255" t="n">
+        <x:v>10.4</x:v>
+      </x:c>
+      <x:c r="H97" s="255" t="n">
+        <x:v>10.4</x:v>
+      </x:c>
+      <x:c r="I97" s="256" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="J97" s="253" t="str">
+        <x:v>亿恒电子888</x:v>
+      </x:c>
+      <x:c r="K97" s="259" t="str">
+        <x:v>CPI-POWER-001</x:v>
+      </x:c>
+      <x:c r="L97" s="259" t="str">
+        <x:v>部分使用</x:v>
+      </x:c>
+      <x:c r="M97" s="259" t="str">
+        <x:v>作为XT60支路并联转接附件；主BOM分电板已由现有设备覆盖，接入前需确认极性和载流能力</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="58" customHeight="1">
+      <x:c r="A98" s="249" t="str">
+        <x:v>ZC-20260902-002</x:v>
+      </x:c>
+      <x:c r="B98" s="249" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C98" s="249" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D98" s="258" t="str">
+        <x:v>XT90公母头延长转接线</x:v>
+      </x:c>
+      <x:c r="E98" s="258" t="str">
+        <x:v>XT90公头转母头 / 10号线 / 30cm</x:v>
+      </x:c>
+      <x:c r="F98" s="250" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G98" s="251" t="n">
+        <x:v>15.7</x:v>
+      </x:c>
+      <x:c r="H98" s="251" t="n">
+        <x:v>15.7</x:v>
+      </x:c>
+      <x:c r="I98" s="252" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="J98" s="249" t="str">
+        <x:v>亿恒电子888</x:v>
+      </x:c>
+      <x:c r="K98" s="258" t="str">
+        <x:v>CPI-POWER-001</x:v>
+      </x:c>
+      <x:c r="L98" s="258" t="str">
+        <x:v>部分使用</x:v>
+      </x:c>
+      <x:c r="M98" s="258" t="str">
+        <x:v>作为XT90输入侧延长转接附件；用途关联分电板供电链路，不改变主BOM需求数量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="58" customHeight="1">
+      <x:c r="A99" s="245" t="str">
+        <x:v>ZC-20260902-003</x:v>
+      </x:c>
+      <x:c r="B99" s="245" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C99" s="245" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D99" s="257" t="str">
+        <x:v>4S平衡充电延长线（第1条）</x:v>
+      </x:c>
+      <x:c r="E99" s="257" t="str">
+        <x:v>4S（5线）/ 22AWG / 公转母 / 10cm</x:v>
+      </x:c>
+      <x:c r="F99" s="246" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G99" s="247" t="n">
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="H99" s="247" t="n">
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="I99" s="248" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="J99" s="245" t="str">
+        <x:v>尼莱电子</x:v>
+      </x:c>
+      <x:c r="K99" s="257"/>
+      <x:c r="L99" s="257" t="str">
+        <x:v>非本体采购不纳入</x:v>
+      </x:c>
+      <x:c r="M99" s="257" t="str">
+        <x:v>用于4S电池平衡充电延长，属于充电附件，不计入单台机器人本体BOM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="58" customHeight="1">
+      <x:c r="A100" s="249" t="str">
+        <x:v>ZC-20260902-004</x:v>
+      </x:c>
+      <x:c r="B100" s="249" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C100" s="249" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D100" s="258" t="str">
+        <x:v>4S平衡充电延长线（第2条）</x:v>
+      </x:c>
+      <x:c r="E100" s="258" t="str">
+        <x:v>4S（5线）/ 22AWG / 公转母 / 10cm</x:v>
+      </x:c>
+      <x:c r="F100" s="250" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G100" s="251" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="H100" s="251" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="I100" s="252" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="J100" s="249" t="str">
+        <x:v>尼莱电子</x:v>
+      </x:c>
+      <x:c r="K100" s="258"/>
+      <x:c r="L100" s="258" t="str">
+        <x:v>非本体采购不纳入</x:v>
+      </x:c>
+      <x:c r="M100" s="258" t="str">
+        <x:v>用于4S电池平衡充电延长；截图规格文字相同，按订单第2条单列，不计入单台机器人本体BOM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="58" customHeight="1">
+      <x:c r="A101" s="253" t="str">
+        <x:v>ZC-20260902-005</x:v>
+      </x:c>
+      <x:c r="B101" s="253" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C101" s="253" t="str">
+        <x:v>可周转资产</x:v>
+      </x:c>
+      <x:c r="D101" s="259" t="str">
+        <x:v>IMAX B6AC 80W平衡充电器</x:v>
+      </x:c>
+      <x:c r="E101" s="259" t="str">
+        <x:v>B6AC+XT90线 / 内置电源 / 80W</x:v>
+      </x:c>
+      <x:c r="F101" s="254" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G101" s="255" t="n">
+        <x:v>89.99</x:v>
+      </x:c>
+      <x:c r="H101" s="255" t="n">
+        <x:v>89.99</x:v>
+      </x:c>
+      <x:c r="I101" s="256" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="J101" s="253" t="str">
+        <x:v>星星模型配件</x:v>
+      </x:c>
+      <x:c r="K101" s="259"/>
+      <x:c r="L101" s="259" t="str">
+        <x:v>通用工具不纳入</x:v>
+      </x:c>
+      <x:c r="M101" s="259" t="str">
+        <x:v>用于动力电池充电与调试，属于外部可周转设备，不计入单台机器人本体BOM</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:M1"/>
@@ -9700,7 +10219,7 @@
     <x:cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="部分使用"/>
     <x:cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="不纳入"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="7">
+  <x:dataValidations count="9">
     <x:dataValidation type="list" sqref="L6:L62">
       <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入"</x:formula1>
     </x:dataValidation>
@@ -9722,10 +10241,16 @@
     <x:dataValidation type="list" sqref="L86:L92">
       <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入,待BOM确认"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="L93:L97">
+      <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入,待BOM确认"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="L93:L101">
+      <x:formula1>"直接使用,部分使用,装配耗材,通用工具不纳入,非本体采购不纳入,待BOM确认"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27b4fcec68e54ef9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f68738d42f241ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
